--- a/Edmund-Viray/viray_Ex3A_tables.xlsx
+++ b/Edmund-Viray/viray_Ex3A_tables.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edmundviray\Documents\DATA_Labs\W2_Workshop\Edmund-Viray\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58BEE6B1-5997-4656-BD37-08DF8AC5CF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966F5CDB-2F66-44D0-BB9D-DF3F4BF93A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A1A22911-0332-417D-9F29-FFA9B8063EE2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{A1A22911-0332-417D-9F29-FFA9B8063EE2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Customer Info" sheetId="1" r:id="rId1"/>
+    <sheet name="Pet Info" sheetId="2" r:id="rId2"/>
+    <sheet name="Services" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,6 +37,53 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>PhoneNumber</t>
+  </si>
+  <si>
+    <t>PaymentMethod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CustomerID </t>
+  </si>
+  <si>
+    <t>PetID</t>
+  </si>
+  <si>
+    <t>CustomerID</t>
+  </si>
+  <si>
+    <t>PetName</t>
+  </si>
+  <si>
+    <t>PetBreed</t>
+  </si>
+  <si>
+    <t>PetColor</t>
+  </si>
+  <si>
+    <t>SessionID</t>
+  </si>
+  <si>
+    <t>SessionRate</t>
+  </si>
+  <si>
+    <t>SessionDate</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
@@ -46,12 +95,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -66,8 +127,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,9 +465,100 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D510CBB-DA8B-426B-A1F8-DB7E04A0D47C}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99CD4E35-AE98-4D45-8458-F898FA766207}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC826124-DBF5-4C76-9332-00165230B1C0}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>